--- a/templates/입력2_연간근무표_2026-08.xlsx
+++ b/templates/입력2_연간근무표_2026-08.xlsx
@@ -680,9 +680,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
@@ -2568,7 +2566,7 @@
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>D,E,N</t>
+          <t>D,E,N,prn</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr"/>
@@ -7511,7 +7509,7 @@
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>D,E,N</t>
+          <t>D,E,N,prn</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr"/>
@@ -10164,7 +10162,7 @@
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>D,E,N</t>
+          <t>D,E,N,prn</t>
         </is>
       </c>
       <c r="F28" s="9" t="inlineStr"/>
@@ -13196,7 +13194,7 @@
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>D,E,N</t>
+          <t>D,E,N,prn</t>
         </is>
       </c>
       <c r="F36" s="9" t="inlineStr"/>
@@ -16586,6 +16584,7 @@
         </is>
       </c>
     </row>
+    <row r="45"/>
     <row r="46">
       <c r="B46" s="20" t="inlineStr">
         <is>

--- a/templates/입력2_연간근무표_2026-08.xlsx
+++ b/templates/입력2_연간근무표_2026-08.xlsx
@@ -557,14 +557,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>입력③ 연간근무표 — 양식 안내</t>
+          <t>입력② 연간근무표 — 양식 안내</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>다월 자동 연동용 파일입니다. 지난달 생성 후 받은 '연간근무표'를 그대로 다시 올리면, 인원 명단·누적 통계(야간·근무일·OFF 등 형평성 지표)뿐 아니라 전월이월값(마지막 근무·연속근무일수·야간블록 등)까지 이번 달 생성에 자동으로 이어집니다 — 예전의 '입력③ 월간근무표(전월)'을 따로 올릴 필요가 없어졌습니다.</t>
+          <t>다월 자동 연동용 파일입니다. 지난달 생성 후 받은 '연간근무표'(출력②)를 그대로 다시 올리면, 인원 명단·누적 통계(야간·근무일·OFF 등 형평성 지표)뿐 아니라 전월이월값(마지막 근무·연속근무일수·야간블록 등)까지 이번 달 생성에 자동으로 이어집니다 — 지난달 월간근무표를 따로 올릴 필요가 없습니다.</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>· 인원 정보 — 순번·이름·직급·숙련도·가능근무·비고·전입·전입일. 파트장이 맨 위, 나머지는 입력①에 등록된 순서 그대로 나열됩니다.</t>
+          <t>· 인원 정보 — 순번·이름·직급·숙련도·가능근무·비고·전입·전입일. 파트장이 맨 위, 나머지는 입력①(원티드표)에 등록된 순서 그대로 나열됩니다.</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>① 기존 인원 목록 바로 아래(맨 아래 '레벨평균' 줄보다 위)에 행을 추가하고 이름·직급·숙련도·가능근무를 적습니다. 이름은 입력②(원티드표)와 정확히 같아야 합니다.</t>
+          <t>① 기존 인원 목록 바로 아래(맨 아래 'D 인원'~'Lv1-3' 통계 줄보다 위)에 행을 추가하고 이름·직급·숙련도·가능근무를 적습니다. 이름은 입력①(원티드표)과 정확히 같아야 합니다.</t>
         </is>
       </c>
     </row>
@@ -662,7 +662,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>따로 적으실 게 없습니다. 입력②(이번 달 명단)에 없으면 자동으로 전출로 보고 이번 달 배정에서 빼며, 그동안 쌓인 이력은 아래쪽 '전출' 구분 행 밑에 그대로 보존됩니다.</t>
+          <t>따로 적으실 게 없습니다. 입력①(원티드표, 이번 달 명단)에 없으면 자동으로 전출로 보고 이번 달 배정에서 빼며, 그동안 쌓인 이력은 아래쪽 '전출' 구분 행 밑에 그대로 보존됩니다.</t>
         </is>
       </c>
     </row>
@@ -676,11 +676,10 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>이 파일 없이 생략해도 됩니다 — 입력①②만으로 근무표 생성이 가능하고, 이 앱이 매달 자동으로 연간근무표를 만들어 드리니 다음 달부터 이어받으면 됩니다.</t>
+          <t>이 파일 없이 생략해도 됩니다 — 입력①(원티드표)만으로 근무표 생성이 가능하고, 이 앱이 매달 자동으로 연간근무표를 만들어 드리니 다음 달부터 이어받으면 됩니다.</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
@@ -16584,7 +16583,6 @@
         </is>
       </c>
     </row>
-    <row r="45"/>
     <row r="46">
       <c r="B46" s="20" t="inlineStr">
         <is>

--- a/templates/입력2_연간근무표_2026-08.xlsx
+++ b/templates/입력2_연간근무표_2026-08.xlsx
@@ -1420,7 +1420,7 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>파트장</t>
+          <t>파트장이름</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>이름01</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>이름02</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>이름03</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
@@ -2948,7 +2948,7 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>이름04</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>이름05</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>이름06</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>이름07</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>이름08</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>이름09</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="B15" s="18" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>이름10</t>
         </is>
       </c>
       <c r="C15" s="18" t="inlineStr">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>이름11</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
@@ -6012,7 +6012,7 @@
       </c>
       <c r="B17" s="18" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>이름12</t>
         </is>
       </c>
       <c r="C17" s="18" t="inlineStr">
@@ -6398,7 +6398,7 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>이름13</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>이름14</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>이름15</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
@@ -7548,7 +7548,7 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>이름16</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>이름17</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
@@ -8312,7 +8312,7 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>이름18</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>이름19</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
@@ -9076,7 +9076,7 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>이름20</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
@@ -9458,7 +9458,7 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>이름21</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
@@ -9840,7 +9840,7 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>이름22</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
@@ -10222,7 +10222,7 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>이름23</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>이름24</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
@@ -10986,7 +10986,7 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>이름25</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
@@ -11368,7 +11368,7 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>이름26</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
@@ -11750,7 +11750,7 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>이름27</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
@@ -12132,7 +12132,7 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>이름28</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
@@ -12514,7 +12514,7 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>이름29</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
@@ -12896,7 +12896,7 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>이름30</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
@@ -13278,7 +13278,7 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>이름31</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
@@ -13660,7 +13660,7 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>이름32</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
@@ -14042,7 +14042,7 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>이름33</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
@@ -14424,7 +14424,7 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>이름34</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
@@ -14806,7 +14806,7 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>이름35</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
@@ -15188,7 +15188,7 @@
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>이름36</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
@@ -15570,7 +15570,7 @@
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>이름37</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
@@ -15952,7 +15952,7 @@
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>이름38</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
@@ -16334,7 +16334,7 @@
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>이름39</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">

--- a/templates/입력2_연간근무표_2026-08.xlsx
+++ b/templates/입력2_연간근무표_2026-08.xlsx
@@ -548,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:A21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -592,96 +592,103 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>· 누적 통계 — 누적야간·누적근무일·누적오프·누적주말야간·누적2일블록·누적3일블록·반영개월수·최근야간점수(참고용)·누적D·누적E·누적prn·누적주말휴일오프·전월잔휴·잔휴. 형평성(균등 배정)을 판단하는 데 참고로 쓰이며, 매달 생성할 때마다 자동 갱신됩니다.</t>
+          <t>· 가능근무 칸에는 근무코드(D·E·N·prn 등) 외에 '2N'·'3N'·'지정'이 함께 적혀 있을 수 있습니다. 2N·3N은 야간을 며칠씩 묶어 설지(안 적으면 2N), '지정'은 근무인력 표의 '지정' 인원으로 셀 수 있는 사람이라는 표시입니다. 이 파일을 다시 올리면 그대로 이어지고, 여기서 고치셔도 됩니다 — 지우면 다음 달부터 그 표시가 없어집니다.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>· 연간 근무 그리드 — 1월 1일부터 지금까지의 근무 이력. 화면에는 참고용으로만 보이지만, 이 중 가장 최근 한 달치는 전월이월값(연속근무일수·말일연속야간 등)을 자동으로 역산하는 데 실제로 쓰입니다.</t>
+          <t>· 누적 통계 — 누적야간·누적근무일·누적오프·누적주말야간·누적2일블록·누적3일블록·반영개월수·최근야간점수(참고용)·누적D·누적E·누적prn·누적주말휴일오프·전월잔휴·잔휴. 형평성(균등 배정)을 판단하는 데 참고로 쓰이며, 매달 생성할 때마다 자동 갱신됩니다.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>전입자(다른 병동에서 오신 분)를 넣을 때</t>
+          <t>· 연간 근무 그리드 — 1월 1일부터 지금까지의 근무 이력. 화면에는 참고용으로만 보이지만, 이 중 가장 최근 한 달치는 전월이월값(연속근무일수·말일연속야간 등)을 자동으로 역산하는 데 실제로 쓰입니다.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>① 기존 인원 목록 바로 아래(맨 아래 'D 인원'~'Lv1-3' 통계 줄보다 위)에 행을 추가하고 이름·직급·숙련도·가능근무를 적습니다. 이름은 입력①(원티드표)과 정확히 같아야 합니다.</t>
+          <t>전입자(다른 병동에서 오신 분)를 넣을 때</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>② '전입' 칸을 클릭해 드롭다운에서 '전입'을 고릅니다(직접 타이핑하지 않아도 됩니다).</t>
+          <t>① 기존 인원 목록 바로 아래(맨 아래 'D 인원'~'Lv1-3' 통계 줄보다 위)에 행을 추가하고 이름·직급·숙련도·가능근무를 적습니다. 이름은 입력①(원티드표)과 정확히 같아야 합니다.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>③ 월중에 오신 분이면 '전입일' 칸에 날짜를 넣습니다. 비워두면 그 달 1일자 전입으로 봅니다.</t>
+          <t>② '전입' 칸을 클릭해 드롭다운에서 '전입'을 고릅니다(직접 타이핑하지 않아도 됩니다).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>④ 전 병동 근무기록을 받아오셨으면 날짜 칸에 날짜를 맞춰 붙여넣습니다(최소 직전 1개월, 3개월이면 야간 형평성까지 정확해집니다). 야간 후 휴식 규칙이 첫날부터 지켜지므로 가능하면 꼭 넣어주세요.</t>
+          <t>③ 월중에 오신 분이면 '전입일' 칸에 날짜를 넣습니다. 비워두면 그 달 1일자 전입으로 봅니다.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>⑤ '전월잔휴'와 '잔휴' 칸에 전 병동에서 넘겨받은 숫자를 적습니다. 잔휴는 근무표만으로는 계산되지 않는 값이라 이것만은 직접 넣어주셔야 합니다(비우면 0으로 보고 진행하며 업로드 직후 화면에 안내가 뜹니다).</t>
+          <t>④ 전 병동 근무기록을 받아오셨으면 날짜 칸에 날짜를 맞춰 붙여넣습니다(최소 직전 1개월, 3개월이면 야간 형평성까지 정확해집니다). 야간 후 휴식 규칙이 첫날부터 지켜지므로 가능하면 꼭 넣어주세요.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>⑥ 누적야간·반영개월수 같은 누적 통계 칸은 비워두세요 — 부서 누적 실적은 우리 병동에 오신 시점부터 0에서 시작합니다.</t>
+          <t>⑤ '전월잔휴'와 '잔휴' 칸에 전 병동에서 넘겨받은 숫자를 적습니다. 잔휴는 근무표만으로는 계산되지 않는 값이라 이것만은 직접 넣어주셔야 합니다(비우면 0으로 보고 진행하며 업로드 직후 화면에 안내가 뜹니다).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>전출자(이번 달 명단에서 빠진 분)</t>
+          <t>⑥ 누적야간·반영개월수 같은 누적 통계 칸은 비워두세요 — 부서 누적 실적은 우리 병동에 오신 시점부터 0에서 시작합니다.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>따로 적으실 게 없습니다. 입력①(원티드표, 이번 달 명단)에 없으면 자동으로 전출로 보고 이번 달 배정에서 빼며, 그동안 쌓인 이력은 아래쪽 '전출' 구분 행 밑에 그대로 보존됩니다.</t>
+          <t>전출자(이번 달 명단에서 빠진 분)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>처음 쓰는 병동이라면</t>
+          <t>따로 적으실 게 없습니다. 입력①(원티드표, 이번 달 명단)에 없으면 자동으로 전출로 보고 이번 달 배정에서 빼며, 그동안 쌓인 이력은 아래쪽 '전출' 구분 행 밑에 그대로 보존됩니다.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>처음 쓰는 병동이라면</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>이 파일 없이 생략해도 됩니다 — 입력①(원티드표)만으로 근무표 생성이 가능하고, 이 앱이 매달 자동으로 연간근무표를 만들어 드리니 다음 달부터 이어받으면 됩니다.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>· '전월잔휴'는 이번 달을 시작할 때의 잔여 휴가, '잔휴'는 이번 달을 반영한 뒤의 잔여입니다(병원 OCS의 '전월 잔휴 / 잔휴' 두 칸과 같은 짝). 배정에 실제로 쓰이는 것은 '잔휴'이고, '전월잔휴'는 OCS에서 옮겨 적어 두는 참고 칸입니다.</t>
         </is>
@@ -1817,7 +1824,7 @@
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>D,E,N</t>
+          <t>D,E,N,지정</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr"/>
@@ -2199,7 +2206,7 @@
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>D,E,N</t>
+          <t>D,E,N,지정</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr"/>
@@ -2581,7 +2588,7 @@
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>D,E,N,prn</t>
+          <t>D,E,N,prn,3N</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr"/>
@@ -3731,7 +3738,7 @@
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>D,E,N</t>
+          <t>D,E,N,2N</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr"/>

--- a/templates/입력2_연간근무표_2026-08.xlsx
+++ b/templates/입력2_연간근무표_2026-08.xlsx
@@ -869,12 +869,12 @@
       </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>누적2일블록</t>
+          <t>누적 2일 블록 야간</t>
         </is>
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>누적3일블록</t>
+          <t>누적 3일 블록 야간</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="T3" s="4" t="inlineStr">
         <is>
-          <t>누적주말휴일오프</t>
+          <t>누적주말휴일오프_total(설,추석 포함)</t>
         </is>
       </c>
       <c r="U3" s="4" t="inlineStr">
@@ -16717,7 +16717,6 @@
         </is>
       </c>
     </row>
-    <row r="45"/>
     <row r="46">
       <c r="B46" s="20" t="inlineStr">
         <is>
